--- a/experiments/3.trace_length_performance_cliff/results/tables/cost.xlsx
+++ b/experiments/3.trace_length_performance_cliff/results/tables/cost.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L937"/>
+  <dimension ref="A1:L1127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47266,6 +47266,9506 @@
         </is>
       </c>
     </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>29.json</t>
+        </is>
+      </c>
+      <c r="D938" t="n">
+        <v>47.70131494401721</v>
+      </c>
+      <c r="E938" t="n">
+        <v>64371</v>
+      </c>
+      <c r="F938" t="n">
+        <v>212</v>
+      </c>
+      <c r="G938" t="n">
+        <v>32</v>
+      </c>
+      <c r="H938" t="n">
+        <v>101.1875</v>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>DataVerification_Expert</t>
+        </is>
+      </c>
+      <c r="K938" t="n">
+        <v>8</v>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>30.json</t>
+        </is>
+      </c>
+      <c r="D939" t="n">
+        <v>21.66163823404349</v>
+      </c>
+      <c r="E939" t="n">
+        <v>23276</v>
+      </c>
+      <c r="F939" t="n">
+        <v>103</v>
+      </c>
+      <c r="G939" t="n">
+        <v>19</v>
+      </c>
+      <c r="H939" t="n">
+        <v>172.1052631578947</v>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K939" t="n">
+        <v>11</v>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>31.json</t>
+        </is>
+      </c>
+      <c r="D940" t="n">
+        <v>48.30474150291411</v>
+      </c>
+      <c r="E940" t="n">
+        <v>65965</v>
+      </c>
+      <c r="F940" t="n">
+        <v>243</v>
+      </c>
+      <c r="G940" t="n">
+        <v>33</v>
+      </c>
+      <c r="H940" t="n">
+        <v>96.57575757575758</v>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K940" t="n">
+        <v>9</v>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>32.json</t>
+        </is>
+      </c>
+      <c r="D941" t="n">
+        <v>9.18939988798229</v>
+      </c>
+      <c r="E941" t="n">
+        <v>6336</v>
+      </c>
+      <c r="F941" t="n">
+        <v>53</v>
+      </c>
+      <c r="G941" t="n">
+        <v>9</v>
+      </c>
+      <c r="H941" t="n">
+        <v>101</v>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K941" t="n">
+        <v>8</v>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>33.json</t>
+        </is>
+      </c>
+      <c r="D942" t="n">
+        <v>30.51898359198822</v>
+      </c>
+      <c r="E942" t="n">
+        <v>32398</v>
+      </c>
+      <c r="F942" t="n">
+        <v>157</v>
+      </c>
+      <c r="G942" t="n">
+        <v>21</v>
+      </c>
+      <c r="H942" t="n">
+        <v>90.57142857142857</v>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K942" t="n">
+        <v>3</v>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>34.json</t>
+        </is>
+      </c>
+      <c r="D943" t="n">
+        <v>74.92677860875847</v>
+      </c>
+      <c r="E943" t="n">
+        <v>119955</v>
+      </c>
+      <c r="F943" t="n">
+        <v>410</v>
+      </c>
+      <c r="G943" t="n">
+        <v>55</v>
+      </c>
+      <c r="H943" t="n">
+        <v>61.12727272727273</v>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>Verification_Expert</t>
+        </is>
+      </c>
+      <c r="K943" t="n">
+        <v>13</v>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>35.json</t>
+        </is>
+      </c>
+      <c r="D944" t="n">
+        <v>10.64916118991096</v>
+      </c>
+      <c r="E944" t="n">
+        <v>5562</v>
+      </c>
+      <c r="F944" t="n">
+        <v>47</v>
+      </c>
+      <c r="G944" t="n">
+        <v>11</v>
+      </c>
+      <c r="H944" t="n">
+        <v>110.4545454545455</v>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K944" t="n">
+        <v>5</v>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>36.json</t>
+        </is>
+      </c>
+      <c r="D945" t="n">
+        <v>8.067310666025151</v>
+      </c>
+      <c r="E945" t="n">
+        <v>5407</v>
+      </c>
+      <c r="F945" t="n">
+        <v>33</v>
+      </c>
+      <c r="G945" t="n">
+        <v>5</v>
+      </c>
+      <c r="H945" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K945" t="n">
+        <v>3</v>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>37.json</t>
+        </is>
+      </c>
+      <c r="D946" t="n">
+        <v>4.94105765997665</v>
+      </c>
+      <c r="E946" t="n">
+        <v>3593</v>
+      </c>
+      <c r="F946" t="n">
+        <v>32</v>
+      </c>
+      <c r="G946" t="n">
+        <v>5</v>
+      </c>
+      <c r="H946" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K946" t="n">
+        <v>3</v>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>38.json</t>
+        </is>
+      </c>
+      <c r="D947" t="n">
+        <v>19.40517528395867</v>
+      </c>
+      <c r="E947" t="n">
+        <v>19237</v>
+      </c>
+      <c r="F947" t="n">
+        <v>97</v>
+      </c>
+      <c r="G947" t="n">
+        <v>13</v>
+      </c>
+      <c r="H947" t="n">
+        <v>125</v>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K947" t="n">
+        <v>5</v>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>39.json</t>
+        </is>
+      </c>
+      <c r="D948" t="n">
+        <v>15.82269023492699</v>
+      </c>
+      <c r="E948" t="n">
+        <v>14631</v>
+      </c>
+      <c r="F948" t="n">
+        <v>82</v>
+      </c>
+      <c r="G948" t="n">
+        <v>13</v>
+      </c>
+      <c r="H948" t="n">
+        <v>138.7692307692308</v>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>DataVerification_Expert</t>
+        </is>
+      </c>
+      <c r="K948" t="n">
+        <v>9</v>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>40.json</t>
+        </is>
+      </c>
+      <c r="D949" t="n">
+        <v>16.44240479602013</v>
+      </c>
+      <c r="E949" t="n">
+        <v>13918</v>
+      </c>
+      <c r="F949" t="n">
+        <v>91</v>
+      </c>
+      <c r="G949" t="n">
+        <v>11</v>
+      </c>
+      <c r="H949" t="n">
+        <v>116.8181818181818</v>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K949" t="n">
+        <v>5</v>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>41.json</t>
+        </is>
+      </c>
+      <c r="D950" t="n">
+        <v>13.17639595799847</v>
+      </c>
+      <c r="E950" t="n">
+        <v>7281</v>
+      </c>
+      <c r="F950" t="n">
+        <v>59</v>
+      </c>
+      <c r="G950" t="n">
+        <v>11</v>
+      </c>
+      <c r="H950" t="n">
+        <v>150.7272727272727</v>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K950" t="n">
+        <v>7</v>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>42.json</t>
+        </is>
+      </c>
+      <c r="D951" t="n">
+        <v>20.92522166017443</v>
+      </c>
+      <c r="E951" t="n">
+        <v>19403</v>
+      </c>
+      <c r="F951" t="n">
+        <v>112</v>
+      </c>
+      <c r="G951" t="n">
+        <v>23</v>
+      </c>
+      <c r="H951" t="n">
+        <v>91.82608695652173</v>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K951" t="n">
+        <v>3</v>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>43.json</t>
+        </is>
+      </c>
+      <c r="D952" t="n">
+        <v>8.122259396128356</v>
+      </c>
+      <c r="E952" t="n">
+        <v>7002</v>
+      </c>
+      <c r="F952" t="n">
+        <v>45</v>
+      </c>
+      <c r="G952" t="n">
+        <v>15</v>
+      </c>
+      <c r="H952" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K952" t="n">
+        <v>13</v>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>44.json</t>
+        </is>
+      </c>
+      <c r="D953" t="n">
+        <v>18.48988408304285</v>
+      </c>
+      <c r="E953" t="n">
+        <v>22384</v>
+      </c>
+      <c r="F953" t="n">
+        <v>127</v>
+      </c>
+      <c r="G953" t="n">
+        <v>15</v>
+      </c>
+      <c r="H953" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>Verification_Expert</t>
+        </is>
+      </c>
+      <c r="K953" t="n">
+        <v>13</v>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>45.json</t>
+        </is>
+      </c>
+      <c r="D954" t="n">
+        <v>32.8860390149639</v>
+      </c>
+      <c r="E954" t="n">
+        <v>43466</v>
+      </c>
+      <c r="F954" t="n">
+        <v>164</v>
+      </c>
+      <c r="G954" t="n">
+        <v>59</v>
+      </c>
+      <c r="H954" t="n">
+        <v>120.271186440678</v>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K954" t="n">
+        <v>5</v>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>46.json</t>
+        </is>
+      </c>
+      <c r="D955" t="n">
+        <v>18.68761216907296</v>
+      </c>
+      <c r="E955" t="n">
+        <v>24038</v>
+      </c>
+      <c r="F955" t="n">
+        <v>113</v>
+      </c>
+      <c r="G955" t="n">
+        <v>17</v>
+      </c>
+      <c r="H955" t="n">
+        <v>133.0588235294118</v>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K955" t="n">
+        <v>13</v>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>47.json</t>
+        </is>
+      </c>
+      <c r="D956" t="n">
+        <v>79.55629036825849</v>
+      </c>
+      <c r="E956" t="n">
+        <v>121319</v>
+      </c>
+      <c r="F956" t="n">
+        <v>396</v>
+      </c>
+      <c r="G956" t="n">
+        <v>51</v>
+      </c>
+      <c r="H956" t="n">
+        <v>69.6078431372549</v>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K956" t="n">
+        <v>5</v>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>48.json</t>
+        </is>
+      </c>
+      <c r="D957" t="n">
+        <v>8.94243414606899</v>
+      </c>
+      <c r="E957" t="n">
+        <v>7597</v>
+      </c>
+      <c r="F957" t="n">
+        <v>54</v>
+      </c>
+      <c r="G957" t="n">
+        <v>7</v>
+      </c>
+      <c r="H957" t="n">
+        <v>121</v>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K957" t="n">
+        <v>5</v>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>49.json</t>
+        </is>
+      </c>
+      <c r="D958" t="n">
+        <v>10.60475760005647</v>
+      </c>
+      <c r="E958" t="n">
+        <v>9693</v>
+      </c>
+      <c r="F958" t="n">
+        <v>63</v>
+      </c>
+      <c r="G958" t="n">
+        <v>15</v>
+      </c>
+      <c r="H958" t="n">
+        <v>100.7333333333333</v>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>DataVerification_Expert</t>
+        </is>
+      </c>
+      <c r="K958" t="n">
+        <v>13</v>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>50.json</t>
+        </is>
+      </c>
+      <c r="D959" t="n">
+        <v>9.087557586026378</v>
+      </c>
+      <c r="E959" t="n">
+        <v>3017</v>
+      </c>
+      <c r="F959" t="n">
+        <v>19</v>
+      </c>
+      <c r="G959" t="n">
+        <v>11</v>
+      </c>
+      <c r="H959" t="n">
+        <v>134.6363636363636</v>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K959" t="n">
+        <v>5</v>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>51.json</t>
+        </is>
+      </c>
+      <c r="D960" t="n">
+        <v>16.42214115493698</v>
+      </c>
+      <c r="E960" t="n">
+        <v>4262</v>
+      </c>
+      <c r="F960" t="n">
+        <v>34</v>
+      </c>
+      <c r="G960" t="n">
+        <v>10</v>
+      </c>
+      <c r="H960" t="n">
+        <v>131</v>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K960" t="n">
+        <v>5</v>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>52.json</t>
+        </is>
+      </c>
+      <c r="D961" t="n">
+        <v>4.283639932982624</v>
+      </c>
+      <c r="E961" t="n">
+        <v>2173</v>
+      </c>
+      <c r="F961" t="n">
+        <v>14</v>
+      </c>
+      <c r="G961" t="n">
+        <v>58</v>
+      </c>
+      <c r="H961" t="n">
+        <v>175.0689655172414</v>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K961" t="n">
+        <v>1</v>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>53.json</t>
+        </is>
+      </c>
+      <c r="D962" t="n">
+        <v>89.47250764799537</v>
+      </c>
+      <c r="E962" t="n">
+        <v>111976</v>
+      </c>
+      <c r="F962" t="n">
+        <v>440</v>
+      </c>
+      <c r="G962" t="n">
+        <v>59</v>
+      </c>
+      <c r="H962" t="n">
+        <v>48.59322033898305</v>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K962" t="n">
+        <v>3</v>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>54.json</t>
+        </is>
+      </c>
+      <c r="D963" t="n">
+        <v>19.67710407200502</v>
+      </c>
+      <c r="E963" t="n">
+        <v>23602</v>
+      </c>
+      <c r="F963" t="n">
+        <v>122</v>
+      </c>
+      <c r="G963" t="n">
+        <v>17</v>
+      </c>
+      <c r="H963" t="n">
+        <v>122.4705882352941</v>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K963" t="n">
+        <v>9</v>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>55.json</t>
+        </is>
+      </c>
+      <c r="D964" t="n">
+        <v>16.52460566407535</v>
+      </c>
+      <c r="E964" t="n">
+        <v>9870</v>
+      </c>
+      <c r="F964" t="n">
+        <v>66</v>
+      </c>
+      <c r="G964" t="n">
+        <v>11</v>
+      </c>
+      <c r="H964" t="n">
+        <v>186.7272727272727</v>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K964" t="n">
+        <v>7</v>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>56.json</t>
+        </is>
+      </c>
+      <c r="D965" t="n">
+        <v>11.75966237904504</v>
+      </c>
+      <c r="E965" t="n">
+        <v>7037</v>
+      </c>
+      <c r="F965" t="n">
+        <v>55</v>
+      </c>
+      <c r="G965" t="n">
+        <v>17</v>
+      </c>
+      <c r="H965" t="n">
+        <v>123.6470588235294</v>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K965" t="n">
+        <v>5</v>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>57.json</t>
+        </is>
+      </c>
+      <c r="D966" t="n">
+        <v>11.0710380479577</v>
+      </c>
+      <c r="E966" t="n">
+        <v>7779</v>
+      </c>
+      <c r="F966" t="n">
+        <v>63</v>
+      </c>
+      <c r="G966" t="n">
+        <v>13</v>
+      </c>
+      <c r="H966" t="n">
+        <v>140.6923076923077</v>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K966" t="n">
+        <v>9</v>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>58.json</t>
+        </is>
+      </c>
+      <c r="D967" t="n">
+        <v>96.89021461945958</v>
+      </c>
+      <c r="E967" t="n">
+        <v>142539</v>
+      </c>
+      <c r="F967" t="n">
+        <v>410</v>
+      </c>
+      <c r="G967" t="n">
+        <v>59</v>
+      </c>
+      <c r="H967" t="n">
+        <v>58.6271186440678</v>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K967" t="n">
+        <v>9</v>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>59.json</t>
+        </is>
+      </c>
+      <c r="D968" t="n">
+        <v>3.860078056924976</v>
+      </c>
+      <c r="E968" t="n">
+        <v>2492</v>
+      </c>
+      <c r="F968" t="n">
+        <v>17</v>
+      </c>
+      <c r="G968" t="n">
+        <v>6</v>
+      </c>
+      <c r="H968" t="n">
+        <v>167</v>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K968" t="n">
+        <v>2</v>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>60.json</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>18.32769751898013</v>
+      </c>
+      <c r="E969" t="n">
+        <v>22211</v>
+      </c>
+      <c r="F969" t="n">
+        <v>103</v>
+      </c>
+      <c r="G969" t="n">
+        <v>15</v>
+      </c>
+      <c r="H969" t="n">
+        <v>123.3333333333333</v>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>DataVerification_Expert</t>
+        </is>
+      </c>
+      <c r="K969" t="n">
+        <v>7</v>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>61.json</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>11.7387672640034</v>
+      </c>
+      <c r="E970" t="n">
+        <v>11244</v>
+      </c>
+      <c r="F970" t="n">
+        <v>71</v>
+      </c>
+      <c r="G970" t="n">
+        <v>9</v>
+      </c>
+      <c r="H970" t="n">
+        <v>127.3333333333333</v>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K970" t="n">
+        <v>1</v>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>62.json</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>79.5666761030443</v>
+      </c>
+      <c r="E971" t="n">
+        <v>85827</v>
+      </c>
+      <c r="F971" t="n">
+        <v>248</v>
+      </c>
+      <c r="G971" t="n">
+        <v>37</v>
+      </c>
+      <c r="H971" t="n">
+        <v>107</v>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>CSVHandling_Expert</t>
+        </is>
+      </c>
+      <c r="K971" t="n">
+        <v>13</v>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>63.json</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>22.40834582399111</v>
+      </c>
+      <c r="E972" t="n">
+        <v>23436</v>
+      </c>
+      <c r="F972" t="n">
+        <v>120</v>
+      </c>
+      <c r="G972" t="n">
+        <v>15</v>
+      </c>
+      <c r="H972" t="n">
+        <v>130.3333333333333</v>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K972" t="n">
+        <v>13</v>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>64.json</t>
+        </is>
+      </c>
+      <c r="D973" t="n">
+        <v>20.32536362600513</v>
+      </c>
+      <c r="E973" t="n">
+        <v>10179</v>
+      </c>
+      <c r="F973" t="n">
+        <v>75</v>
+      </c>
+      <c r="G973" t="n">
+        <v>11</v>
+      </c>
+      <c r="H973" t="n">
+        <v>119.2727272727273</v>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K973" t="n">
+        <v>9</v>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>65.json</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>9.625819930923171</v>
+      </c>
+      <c r="E974" t="n">
+        <v>11480</v>
+      </c>
+      <c r="F974" t="n">
+        <v>63</v>
+      </c>
+      <c r="G974" t="n">
+        <v>11</v>
+      </c>
+      <c r="H974" t="n">
+        <v>168.3636363636364</v>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>Verification_Expert</t>
+        </is>
+      </c>
+      <c r="K974" t="n">
+        <v>9</v>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>66.json</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>4.66575850098161</v>
+      </c>
+      <c r="E975" t="n">
+        <v>2989</v>
+      </c>
+      <c r="F975" t="n">
+        <v>20</v>
+      </c>
+      <c r="G975" t="n">
+        <v>7</v>
+      </c>
+      <c r="H975" t="n">
+        <v>169</v>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K975" t="n">
+        <v>1</v>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>67.json</t>
+        </is>
+      </c>
+      <c r="D976" t="n">
+        <v>30.66448433313053</v>
+      </c>
+      <c r="E976" t="n">
+        <v>15965</v>
+      </c>
+      <c r="F976" t="n">
+        <v>101</v>
+      </c>
+      <c r="G976" t="n">
+        <v>15</v>
+      </c>
+      <c r="H976" t="n">
+        <v>116.7333333333333</v>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K976" t="n">
+        <v>5</v>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>68.json</t>
+        </is>
+      </c>
+      <c r="D977" t="n">
+        <v>14.22517752100248</v>
+      </c>
+      <c r="E977" t="n">
+        <v>6899</v>
+      </c>
+      <c r="F977" t="n">
+        <v>38</v>
+      </c>
+      <c r="G977" t="n">
+        <v>10</v>
+      </c>
+      <c r="H977" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K977" t="n">
+        <v>2</v>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>69.json</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>22.09192496299511</v>
+      </c>
+      <c r="E978" t="n">
+        <v>8091</v>
+      </c>
+      <c r="F978" t="n">
+        <v>73</v>
+      </c>
+      <c r="G978" t="n">
+        <v>27</v>
+      </c>
+      <c r="H978" t="n">
+        <v>72.07407407407408</v>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K978" t="n">
+        <v>9</v>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>70.json</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>30.97133644402493</v>
+      </c>
+      <c r="E979" t="n">
+        <v>33918</v>
+      </c>
+      <c r="F979" t="n">
+        <v>158</v>
+      </c>
+      <c r="G979" t="n">
+        <v>22</v>
+      </c>
+      <c r="H979" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K979" t="n">
+        <v>6</v>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>71.json</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>57.2107773218886</v>
+      </c>
+      <c r="E980" t="n">
+        <v>59836</v>
+      </c>
+      <c r="F980" t="n">
+        <v>192</v>
+      </c>
+      <c r="G980" t="n">
+        <v>36</v>
+      </c>
+      <c r="H980" t="n">
+        <v>125.6944444444444</v>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K980" t="n">
+        <v>8</v>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>72.json</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>59.03342153708218</v>
+      </c>
+      <c r="E981" t="n">
+        <v>81040</v>
+      </c>
+      <c r="F981" t="n">
+        <v>309</v>
+      </c>
+      <c r="G981" t="n">
+        <v>57</v>
+      </c>
+      <c r="H981" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K981" t="n">
+        <v>11</v>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>73.json</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>5.090666375996079</v>
+      </c>
+      <c r="E982" t="n">
+        <v>4912</v>
+      </c>
+      <c r="F982" t="n">
+        <v>34</v>
+      </c>
+      <c r="G982" t="n">
+        <v>9</v>
+      </c>
+      <c r="H982" t="n">
+        <v>129.8888888888889</v>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K982" t="n">
+        <v>1</v>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>74.json</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>14.61951354594203</v>
+      </c>
+      <c r="E983" t="n">
+        <v>14094</v>
+      </c>
+      <c r="F983" t="n">
+        <v>82</v>
+      </c>
+      <c r="G983" t="n">
+        <v>59</v>
+      </c>
+      <c r="H983" t="n">
+        <v>60.45762711864407</v>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K983" t="n">
+        <v>7</v>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>75.json</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>12.56386413000291</v>
+      </c>
+      <c r="E984" t="n">
+        <v>11190</v>
+      </c>
+      <c r="F984" t="n">
+        <v>78</v>
+      </c>
+      <c r="G984" t="n">
+        <v>9</v>
+      </c>
+      <c r="H984" t="n">
+        <v>125.7777777777778</v>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K984" t="n">
+        <v>1</v>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>76.json</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>18.92858758196235</v>
+      </c>
+      <c r="E985" t="n">
+        <v>14707</v>
+      </c>
+      <c r="F985" t="n">
+        <v>87</v>
+      </c>
+      <c r="G985" t="n">
+        <v>11</v>
+      </c>
+      <c r="H985" t="n">
+        <v>124.5454545454545</v>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K985" t="n">
+        <v>9</v>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>77.json</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>10.90100603993051</v>
+      </c>
+      <c r="E986" t="n">
+        <v>10677</v>
+      </c>
+      <c r="F986" t="n">
+        <v>71</v>
+      </c>
+      <c r="G986" t="n">
+        <v>21</v>
+      </c>
+      <c r="H986" t="n">
+        <v>130.2857142857143</v>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K986" t="n">
+        <v>3</v>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>78.json</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>20.82146422105143</v>
+      </c>
+      <c r="E987" t="n">
+        <v>17689</v>
+      </c>
+      <c r="F987" t="n">
+        <v>123</v>
+      </c>
+      <c r="G987" t="n">
+        <v>48</v>
+      </c>
+      <c r="H987" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K987" t="n">
+        <v>8</v>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>79.json</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>5.797137725981884</v>
+      </c>
+      <c r="E988" t="n">
+        <v>4864</v>
+      </c>
+      <c r="F988" t="n">
+        <v>32</v>
+      </c>
+      <c r="G988" t="n">
+        <v>15</v>
+      </c>
+      <c r="H988" t="n">
+        <v>140.8666666666667</v>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>WebServing_Expert</t>
+        </is>
+      </c>
+      <c r="K988" t="n">
+        <v>9</v>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>80.json</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>6.574326165078674</v>
+      </c>
+      <c r="E989" t="n">
+        <v>5977</v>
+      </c>
+      <c r="F989" t="n">
+        <v>35</v>
+      </c>
+      <c r="G989" t="n">
+        <v>7</v>
+      </c>
+      <c r="H989" t="n">
+        <v>173.7142857142857</v>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>DataVerification_Expert</t>
+        </is>
+      </c>
+      <c r="K989" t="n">
+        <v>5</v>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>81.json</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>6.658407168055419</v>
+      </c>
+      <c r="E990" t="n">
+        <v>6197</v>
+      </c>
+      <c r="F990" t="n">
+        <v>38</v>
+      </c>
+      <c r="G990" t="n">
+        <v>10</v>
+      </c>
+      <c r="H990" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K990" t="n">
+        <v>9</v>
+      </c>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>82.json</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>24.14445444894955</v>
+      </c>
+      <c r="E991" t="n">
+        <v>27572</v>
+      </c>
+      <c r="F991" t="n">
+        <v>119</v>
+      </c>
+      <c r="G991" t="n">
+        <v>29</v>
+      </c>
+      <c r="H991" t="n">
+        <v>119.6551724137931</v>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>InformationExtraction_Expert</t>
+        </is>
+      </c>
+      <c r="K991" t="n">
+        <v>15</v>
+      </c>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>83.json</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>6.933571567060426</v>
+      </c>
+      <c r="E992" t="n">
+        <v>7388</v>
+      </c>
+      <c r="F992" t="n">
+        <v>41</v>
+      </c>
+      <c r="G992" t="n">
+        <v>7</v>
+      </c>
+      <c r="H992" t="n">
+        <v>167.2857142857143</v>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>Verification_Expert</t>
+        </is>
+      </c>
+      <c r="K992" t="n">
+        <v>5</v>
+      </c>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>84.json</t>
+        </is>
+      </c>
+      <c r="D993" t="n">
+        <v>4.977930655993987</v>
+      </c>
+      <c r="E993" t="n">
+        <v>3681</v>
+      </c>
+      <c r="F993" t="n">
+        <v>23</v>
+      </c>
+      <c r="G993" t="n">
+        <v>5</v>
+      </c>
+      <c r="H993" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>CSVHandling_Expert</t>
+        </is>
+      </c>
+      <c r="K993" t="n">
+        <v>3</v>
+      </c>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>85.json</t>
+        </is>
+      </c>
+      <c r="D994" t="n">
+        <v>15.97613524610642</v>
+      </c>
+      <c r="E994" t="n">
+        <v>23395</v>
+      </c>
+      <c r="F994" t="n">
+        <v>86</v>
+      </c>
+      <c r="G994" t="n">
+        <v>47</v>
+      </c>
+      <c r="H994" t="n">
+        <v>165.2127659574468</v>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K994" t="n">
+        <v>11</v>
+      </c>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>86.json</t>
+        </is>
+      </c>
+      <c r="D995" t="n">
+        <v>29.78980353398947</v>
+      </c>
+      <c r="E995" t="n">
+        <v>34190</v>
+      </c>
+      <c r="F995" t="n">
+        <v>124</v>
+      </c>
+      <c r="G995" t="n">
+        <v>20</v>
+      </c>
+      <c r="H995" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K995" t="n">
+        <v>13</v>
+      </c>
+      <c r="L995" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>87.json</t>
+        </is>
+      </c>
+      <c r="D996" t="n">
+        <v>10.76516423100838</v>
+      </c>
+      <c r="E996" t="n">
+        <v>9288</v>
+      </c>
+      <c r="F996" t="n">
+        <v>54</v>
+      </c>
+      <c r="G996" t="n">
+        <v>47</v>
+      </c>
+      <c r="H996" t="n">
+        <v>164.9148936170213</v>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K996" t="n">
+        <v>7</v>
+      </c>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>88.json</t>
+        </is>
+      </c>
+      <c r="D997" t="n">
+        <v>23.26995070400881</v>
+      </c>
+      <c r="E997" t="n">
+        <v>27270</v>
+      </c>
+      <c r="F997" t="n">
+        <v>110</v>
+      </c>
+      <c r="G997" t="n">
+        <v>47</v>
+      </c>
+      <c r="H997" t="n">
+        <v>152.468085106383</v>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K997" t="n">
+        <v>18</v>
+      </c>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>89.json</t>
+        </is>
+      </c>
+      <c r="D998" t="n">
+        <v>38.71000680810539</v>
+      </c>
+      <c r="E998" t="n">
+        <v>52237</v>
+      </c>
+      <c r="F998" t="n">
+        <v>147</v>
+      </c>
+      <c r="G998" t="n">
+        <v>22</v>
+      </c>
+      <c r="H998" t="n">
+        <v>164.5454545454545</v>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K998" t="n">
+        <v>7</v>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>90.json</t>
+        </is>
+      </c>
+      <c r="D999" t="n">
+        <v>21.91248538903892</v>
+      </c>
+      <c r="E999" t="n">
+        <v>28764</v>
+      </c>
+      <c r="F999" t="n">
+        <v>99</v>
+      </c>
+      <c r="G999" t="n">
+        <v>23</v>
+      </c>
+      <c r="H999" t="n">
+        <v>173.6521739130435</v>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K999" t="n">
+        <v>15</v>
+      </c>
+      <c r="L999" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>91.json</t>
+        </is>
+      </c>
+      <c r="D1000" t="n">
+        <v>15.33835364802508</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>19931</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>71</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>46</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>206.3695652173913</v>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1000" t="n">
+        <v>28</v>
+      </c>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>92.json</t>
+        </is>
+      </c>
+      <c r="D1001" t="n">
+        <v>39.12661546608433</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>85628</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>171.5416666666667</v>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1001" t="n">
+        <v>15</v>
+      </c>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>94.json</t>
+        </is>
+      </c>
+      <c r="D1002" t="n">
+        <v>56.63270777586149</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>110502</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>230</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>177.4146341463415</v>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1002" t="n">
+        <v>14</v>
+      </c>
+      <c r="L1002" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>95.json</t>
+        </is>
+      </c>
+      <c r="D1003" t="n">
+        <v>23.77798136498313</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>34639</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>122</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>155.1578947368421</v>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>Coder</t>
+        </is>
+      </c>
+      <c r="K1003" t="n">
+        <v>36</v>
+      </c>
+      <c r="L1003" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>96.json</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>25.0235048479517</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>34199</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>133.9444444444445</v>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1004" t="n">
+        <v>15</v>
+      </c>
+      <c r="L1004" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>97.json</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>37.25011426879792</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>46982</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>148</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>149.8085106382979</v>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1005" t="n">
+        <v>47</v>
+      </c>
+      <c r="L1005" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>98.json</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>33.50777542911237</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>31410</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>164.7021276595745</v>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1006" t="n">
+        <v>34</v>
+      </c>
+      <c r="L1006" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>99.json</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>18.98106133792317</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>30699</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>105</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1007" t="n">
+        <v>200.6785714285714</v>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1007" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1007" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>100.json</t>
+        </is>
+      </c>
+      <c r="D1008" t="n">
+        <v>11.38495350099402</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>10243</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1008" t="n">
+        <v>200.7741935483871</v>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1008" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1008" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>101.json</t>
+        </is>
+      </c>
+      <c r="D1009" t="n">
+        <v>32.78894169797422</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>44242</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>152</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>137.551724137931</v>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1009" t="n">
+        <v>27</v>
+      </c>
+      <c r="L1009" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>102.json</t>
+        </is>
+      </c>
+      <c r="D1010" t="n">
+        <v>21.24714496399974</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>12677</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>73</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>162.8958333333333</v>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1010" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1010" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>103.json</t>
+        </is>
+      </c>
+      <c r="D1011" t="n">
+        <v>24.83530117420014</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>36223</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>126.9487179487179</v>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1011" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1011" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>104.json</t>
+        </is>
+      </c>
+      <c r="D1012" t="n">
+        <v>13.29018395085586</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>16240</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>208.7272727272727</v>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>FileSurfer</t>
+        </is>
+      </c>
+      <c r="K1012" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1012" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>105.json</t>
+        </is>
+      </c>
+      <c r="D1013" t="n">
+        <v>41.65889106399845</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>80792</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>180.7407407407407</v>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1013" t="n">
+        <v>25</v>
+      </c>
+      <c r="L1013" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>106.json</t>
+        </is>
+      </c>
+      <c r="D1014" t="n">
+        <v>10.93947398813907</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>15080</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>65</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>157.1428571428571</v>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1014" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1014" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>107.json</t>
+        </is>
+      </c>
+      <c r="D1015" t="n">
+        <v>40.32582590711536</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>68435</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>177</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>183.9583333333333</v>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1015" t="n">
+        <v>24</v>
+      </c>
+      <c r="L1015" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>108.json</t>
+        </is>
+      </c>
+      <c r="D1016" t="n">
+        <v>22.074156415998</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>20589</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>89</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>23</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>142.4782608695652</v>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1016" t="n">
+        <v>21</v>
+      </c>
+      <c r="L1016" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>109.json</t>
+        </is>
+      </c>
+      <c r="D1017" t="n">
+        <v>28.53040596592473</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>38800</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>128</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>157.3191489361702</v>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1017" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1017" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>110.json</t>
+        </is>
+      </c>
+      <c r="D1018" t="n">
+        <v>10.65674176596804</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>10228</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>212.8947368421053</v>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1018" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1018" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>111.json</t>
+        </is>
+      </c>
+      <c r="D1019" t="n">
+        <v>2.024681220995262</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>1029</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>208.6666666666667</v>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1019" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1019" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>112.json</t>
+        </is>
+      </c>
+      <c r="D1020" t="n">
+        <v>10.77408879308496</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>12561</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>59</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>156.25</v>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1020" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1020" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>113.json</t>
+        </is>
+      </c>
+      <c r="D1021" t="n">
+        <v>35.16082991583971</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>18140</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>86</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>167.22</v>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1021" t="n">
+        <v>21</v>
+      </c>
+      <c r="L1021" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>114.json</t>
+        </is>
+      </c>
+      <c r="D1022" t="n">
+        <v>10.44681505300105</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>3967</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>169.578947368421</v>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1022" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>115.json</t>
+        </is>
+      </c>
+      <c r="D1023" t="n">
+        <v>6.174304765008856</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>6226</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>253.3846153846154</v>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1023" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1023" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>116.json</t>
+        </is>
+      </c>
+      <c r="D1024" t="n">
+        <v>11.1078417779645</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>9904</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>182.4444444444445</v>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1024" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1024" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>117.json</t>
+        </is>
+      </c>
+      <c r="D1025" t="n">
+        <v>8.182504524011165</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>3465</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>37</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>240.0540540540541</v>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>FileSurfer</t>
+        </is>
+      </c>
+      <c r="K1025" t="n">
+        <v>13</v>
+      </c>
+      <c r="L1025" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>118.json</t>
+        </is>
+      </c>
+      <c r="D1026" t="n">
+        <v>7.135816556983627</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>6120</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>177.25</v>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1026" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1026" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>119.json</t>
+        </is>
+      </c>
+      <c r="D1027" t="n">
+        <v>20.74866053805454</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>25558</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>166.4468085106383</v>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1027" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1027" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>120.json</t>
+        </is>
+      </c>
+      <c r="D1028" t="n">
+        <v>22.53339295799378</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>32101</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>49</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>164.8571428571429</v>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1028" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1028" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>121.json</t>
+        </is>
+      </c>
+      <c r="D1029" t="n">
+        <v>27.1479190121172</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>42050</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>37</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>197.9459459459459</v>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1029" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1029" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>122.json</t>
+        </is>
+      </c>
+      <c r="D1030" t="n">
+        <v>19.5937669640989</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>23862</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>95</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>49</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>144.4285714285714</v>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1030" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>123.json</t>
+        </is>
+      </c>
+      <c r="D1031" t="n">
+        <v>21.7812740499503</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>19221</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>124.9523809523809</v>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1031" t="n">
+        <v>13</v>
+      </c>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>124.json</t>
+        </is>
+      </c>
+      <c r="D1032" t="n">
+        <v>13.60406019201037</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>13467</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>135.8333333333333</v>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1032" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>125.json</t>
+        </is>
+      </c>
+      <c r="D1033" t="n">
+        <v>0.7384797890554182</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>891</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>44</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>195.6136363636364</v>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1033" t="n">
+        <v>29</v>
+      </c>
+      <c r="L1033" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>126.json</t>
+        </is>
+      </c>
+      <c r="D1034" t="n">
+        <v>12.95995591592509</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>13461</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>76</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1034" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>127.json</t>
+        </is>
+      </c>
+      <c r="D1035" t="n">
+        <v>11.46636944497004</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>10595</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>241.2857142857143</v>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1035" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>128.json</t>
+        </is>
+      </c>
+      <c r="D1036" t="n">
+        <v>4.943729878054</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>7293</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>252.8181818181818</v>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>FileSurfer</t>
+        </is>
+      </c>
+      <c r="K1036" t="n">
+        <v>21</v>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>129.json</t>
+        </is>
+      </c>
+      <c r="D1037" t="n">
+        <v>17.52928820194211</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>30925</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>178.8095238095238</v>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1037" t="n">
+        <v>14</v>
+      </c>
+      <c r="L1037" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>130.json</t>
+        </is>
+      </c>
+      <c r="D1038" t="n">
+        <v>32.80970642104512</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>49792</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>46</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>135.1521739130435</v>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1038" t="n">
+        <v>40</v>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>131.json</t>
+        </is>
+      </c>
+      <c r="D1039" t="n">
+        <v>17.82735501707066</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>19884</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>157</v>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1039" t="n">
+        <v>13</v>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>132.json</t>
+        </is>
+      </c>
+      <c r="D1040" t="n">
+        <v>14.98332775215385</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>18748</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>188.08</v>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1040" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>133.json</t>
+        </is>
+      </c>
+      <c r="D1041" t="n">
+        <v>10.04139285592828</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>10582</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1041" t="n">
+        <v>42</v>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>134.json</t>
+        </is>
+      </c>
+      <c r="D1042" t="n">
+        <v>5.698607617989182</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>5910</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1042" t="n">
+        <v>244.8333333333333</v>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1042" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>135.json</t>
+        </is>
+      </c>
+      <c r="D1043" t="n">
+        <v>16.00840039685136</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>14361</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>61</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>161.4791666666667</v>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1043" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>136.json</t>
+        </is>
+      </c>
+      <c r="D1044" t="n">
+        <v>8.763716376037337</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>6119</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>144.9090909090909</v>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1044" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1044" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>137.json</t>
+        </is>
+      </c>
+      <c r="D1045" t="n">
+        <v>10.6551506719552</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>12396</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>55</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1045" t="n">
+        <v>201.1842105263158</v>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1045" t="n">
+        <v>14</v>
+      </c>
+      <c r="L1045" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>138.json</t>
+        </is>
+      </c>
+      <c r="D1046" t="n">
+        <v>37.03340769390343</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>64230</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>173</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>49</v>
+      </c>
+      <c r="H1046" t="n">
+        <v>159.9591836734694</v>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1046" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1046" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>139.json</t>
+        </is>
+      </c>
+      <c r="D1047" t="n">
+        <v>17.24253457807936</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>17530</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1047" t="n">
+        <v>137.6363636363636</v>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1047" t="n">
+        <v>11</v>
+      </c>
+      <c r="L1047" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>140.json</t>
+        </is>
+      </c>
+      <c r="D1048" t="n">
+        <v>15.11384638800519</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>19923</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>80</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1048" t="n">
+        <v>167.3617021276596</v>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1048" t="n">
+        <v>11</v>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>141.json</t>
+        </is>
+      </c>
+      <c r="D1049" t="n">
+        <v>15.72354786214419</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>20577</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>72</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1049" t="n">
+        <v>194.2708333333333</v>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1049" t="n">
+        <v>39</v>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>142.json</t>
+        </is>
+      </c>
+      <c r="D1050" t="n">
+        <v>10.62836916610831</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>12830</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>65</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1050" t="n">
+        <v>132.2857142857143</v>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1050" t="n">
+        <v>24</v>
+      </c>
+      <c r="L1050" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>143.json</t>
+        </is>
+      </c>
+      <c r="D1051" t="n">
+        <v>12.90862761001335</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>9179</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1051" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1051" t="n">
+        <v>11</v>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>144.json</t>
+        </is>
+      </c>
+      <c r="D1052" t="n">
+        <v>39.87983965210151</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>67501</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>175</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>46</v>
+      </c>
+      <c r="H1052" t="n">
+        <v>138.8260869565217</v>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1052" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>145.json</t>
+        </is>
+      </c>
+      <c r="D1053" t="n">
+        <v>10.78574477514485</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>10908</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1053" t="n">
+        <v>148.1</v>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1053" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>146.json</t>
+        </is>
+      </c>
+      <c r="D1054" t="n">
+        <v>12.328012250131</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>16236</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>63</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1054" t="n">
+        <v>153.4468085106383</v>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1054" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1054" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>147.json</t>
+        </is>
+      </c>
+      <c r="D1055" t="n">
+        <v>23.97925964312162</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>36651</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1055" t="n">
+        <v>161.9047619047619</v>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1055" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>148.json</t>
+        </is>
+      </c>
+      <c r="D1056" t="n">
+        <v>10.03895445086528</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>11243</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1056" t="n">
+        <v>187</v>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>FileSurfer</t>
+        </is>
+      </c>
+      <c r="K1056" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1056" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>149.json</t>
+        </is>
+      </c>
+      <c r="D1057" t="n">
+        <v>12.42255054513225</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>9679</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1057" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1057" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1057" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>150.json</t>
+        </is>
+      </c>
+      <c r="D1058" t="n">
+        <v>24.17270841688151</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>44504</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>129</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1058" t="n">
+        <v>141</v>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1058" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1058" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>151.json</t>
+        </is>
+      </c>
+      <c r="D1059" t="n">
+        <v>10.62755662802374</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>14500</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1059" t="n">
+        <v>250.0571428571428</v>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1059" t="n">
+        <v>25</v>
+      </c>
+      <c r="L1059" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>152.json</t>
+        </is>
+      </c>
+      <c r="D1060" t="n">
+        <v>16.24204670509789</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>25195</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>83</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1060" t="n">
+        <v>168</v>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1060" t="n">
+        <v>13</v>
+      </c>
+      <c r="L1060" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>153.json</t>
+        </is>
+      </c>
+      <c r="D1061" t="n">
+        <v>7.202654496999457</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>4867</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1061" t="n">
+        <v>199.2857142857143</v>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1061" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1061" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>154.json</t>
+        </is>
+      </c>
+      <c r="D1062" t="n">
+        <v>46.46213203517254</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>87315</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>220</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1062" t="n">
+        <v>146.25</v>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1062" t="n">
+        <v>24</v>
+      </c>
+      <c r="L1062" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>155.json</t>
+        </is>
+      </c>
+      <c r="D1063" t="n">
+        <v>13.03357324592071</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>8475</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>37</v>
+      </c>
+      <c r="H1063" t="n">
+        <v>214.4054054054054</v>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1063" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1063" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>156.json</t>
+        </is>
+      </c>
+      <c r="D1064" t="n">
+        <v>19.31806501303799</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>11365</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>56</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>173.9090909090909</v>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1064" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1064" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>157.json</t>
+        </is>
+      </c>
+      <c r="D1065" t="n">
+        <v>12.01593431207584</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>14370</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1065" t="n">
+        <v>282.3611111111111</v>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>Coder</t>
+        </is>
+      </c>
+      <c r="K1065" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1065" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>158.json</t>
+        </is>
+      </c>
+      <c r="D1066" t="n">
+        <v>79.08938918192871</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>155708</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>45</v>
+      </c>
+      <c r="H1066" t="n">
+        <v>119.4888888888889</v>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1066" t="n">
+        <v>45</v>
+      </c>
+      <c r="L1066" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>159.json</t>
+        </is>
+      </c>
+      <c r="D1067" t="n">
+        <v>13.76660524395993</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>12836</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>72</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1067" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1067" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1067" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>160.json</t>
+        </is>
+      </c>
+      <c r="D1068" t="n">
+        <v>59.80047760490561</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>96493</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>216</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>150.7659574468085</v>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1068" t="n">
+        <v>47</v>
+      </c>
+      <c r="L1068" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>161.json</t>
+        </is>
+      </c>
+      <c r="D1069" t="n">
+        <v>19.81569368590135</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>19397</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>80</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>45</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>184.4666666666667</v>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1069" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1069" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>162.json</t>
+        </is>
+      </c>
+      <c r="D1070" t="n">
+        <v>58.05705941579072</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>155675</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>253</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>40</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>168.725</v>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1070" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1070" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>163.json</t>
+        </is>
+      </c>
+      <c r="D1071" t="n">
+        <v>12.29175781406229</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>13760</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>65</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>172.2307692307692</v>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1071" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1071" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>164.json</t>
+        </is>
+      </c>
+      <c r="D1072" t="n">
+        <v>14.41380459698848</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>8047</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>197.875</v>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1072" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1072" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>165.json</t>
+        </is>
+      </c>
+      <c r="D1073" t="n">
+        <v>23.55058802803978</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>43239</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>174.0555555555555</v>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>FileSurfer</t>
+        </is>
+      </c>
+      <c r="K1073" t="n">
+        <v>11</v>
+      </c>
+      <c r="L1073" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>166.json</t>
+        </is>
+      </c>
+      <c r="D1074" t="n">
+        <v>17.20833741693059</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>16624</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>148</v>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1074" t="n">
+        <v>12</v>
+      </c>
+      <c r="L1074" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>167.json</t>
+        </is>
+      </c>
+      <c r="D1075" t="n">
+        <v>16.11219862103462</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>22651</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1075" t="n">
+        <v>219.4166666666667</v>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1075" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1075" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>168.json</t>
+        </is>
+      </c>
+      <c r="D1076" t="n">
+        <v>22.75814445887227</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>39452</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>115</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>46</v>
+      </c>
+      <c r="H1076" t="n">
+        <v>185.4347826086957</v>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1076" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1076" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>169.json</t>
+        </is>
+      </c>
+      <c r="D1077" t="n">
+        <v>6.031419899954926</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>5925</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>26</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>148.0384615384615</v>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1077" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1077" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>170.json</t>
+        </is>
+      </c>
+      <c r="D1078" t="n">
+        <v>11.16493836900918</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>9969</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1078" t="n">
+        <v>237.5714285714286</v>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1078" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1078" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>171.json</t>
+        </is>
+      </c>
+      <c r="D1079" t="n">
+        <v>4.840128826966975</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>9662</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1079" t="n">
+        <v>199.6666666666667</v>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1079" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1079" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>172.json</t>
+        </is>
+      </c>
+      <c r="D1080" t="n">
+        <v>14.62560118013062</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>11965</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1080" t="n">
+        <v>151.5384615384615</v>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>WebSurfer</t>
+        </is>
+      </c>
+      <c r="K1080" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1080" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>173.json</t>
+        </is>
+      </c>
+      <c r="D1081" t="n">
+        <v>9.401999663969036</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>10668</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1081" t="n">
+        <v>273.8888888888889</v>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1081" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1081" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>174.json</t>
+        </is>
+      </c>
+      <c r="D1082" t="n">
+        <v>20.09083838411607</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>41092</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1082" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1082" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1082" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1082" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>175.json</t>
+        </is>
+      </c>
+      <c r="D1083" t="n">
+        <v>11.56598074594513</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>20699</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>55</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1083" t="n">
+        <v>317.5333333333334</v>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1083" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1083" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>176.json</t>
+        </is>
+      </c>
+      <c r="D1084" t="n">
+        <v>28.83968411094975</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>21559</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>124</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1084" t="n">
+        <v>34</v>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1084" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1084" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>177.json</t>
+        </is>
+      </c>
+      <c r="D1085" t="n">
+        <v>25.48987985803979</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>26469</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>29.42857142857143</v>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>bash</t>
+        </is>
+      </c>
+      <c r="K1085" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1085" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>178.json</t>
+        </is>
+      </c>
+      <c r="D1086" t="n">
+        <v>14.51502550515579</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>37309</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>114</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1086" t="n">
+        <v>45.76470588235294</v>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1086" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1086" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>179.json</t>
+        </is>
+      </c>
+      <c r="D1087" t="n">
+        <v>29.21282419894123</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>15425</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>146</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1087" t="inlineStr">
+        <is>
+          <t>bash</t>
+        </is>
+      </c>
+      <c r="K1087" t="n">
+        <v>12</v>
+      </c>
+      <c r="L1087" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>180.json</t>
+        </is>
+      </c>
+      <c r="D1088" t="n">
+        <v>12.74667355412384</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>73</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>bash</t>
+        </is>
+      </c>
+      <c r="K1088" t="n">
+        <v>11</v>
+      </c>
+      <c r="L1088" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>181.json</t>
+        </is>
+      </c>
+      <c r="D1089" t="n">
+        <v>34.03393623390002</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>33812</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>153</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>83</v>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1089" t="n">
+        <v>13</v>
+      </c>
+      <c r="L1089" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>182.json</t>
+        </is>
+      </c>
+      <c r="D1090" t="n">
+        <v>3.968510141014121</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>2839</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1090" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1090" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>183.json</t>
+        </is>
+      </c>
+      <c r="D1091" t="n">
+        <v>43.92604060494341</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>44252</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>246</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>26.05555555555556</v>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1091" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1091" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>184.json</t>
+        </is>
+      </c>
+      <c r="D1092" t="n">
+        <v>34.05587662401376</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>38670</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>151</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>37.07894736842105</v>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1092" t="n">
+        <v>32</v>
+      </c>
+      <c r="L1092" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>185.json</t>
+        </is>
+      </c>
+      <c r="D1093" t="n">
+        <v>37.86476944084279</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>28656</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>203</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>37.62068965517241</v>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1093" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1093" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>186.json</t>
+        </is>
+      </c>
+      <c r="D1094" t="n">
+        <v>14.23072393302573</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>19436</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>94</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>94</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>16.97872340425532</v>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1094" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1094" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>187.json</t>
+        </is>
+      </c>
+      <c r="D1095" t="n">
+        <v>24.0593250390375</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>17175</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>109</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>38.86666666666667</v>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>bash</t>
+        </is>
+      </c>
+      <c r="K1095" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1095" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>188.json</t>
+        </is>
+      </c>
+      <c r="D1096" t="n">
+        <v>28.12324070109753</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>15431</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>140</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>31.05555555555556</v>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1096" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1096" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>189.json</t>
+        </is>
+      </c>
+      <c r="D1097" t="n">
+        <v>4.234451536030974</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>4020</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>34.09523809523809</v>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1097" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1097" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>190.json</t>
+        </is>
+      </c>
+      <c r="D1098" t="n">
+        <v>30.02896749100182</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>21545</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>157</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>43.42105263157895</v>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1098" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1098" t="n">
+        <v>32</v>
+      </c>
+      <c r="L1098" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>191.json</t>
+        </is>
+      </c>
+      <c r="D1099" t="n">
+        <v>15.52869994891807</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>11257</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>83</v>
+      </c>
+      <c r="H1099" t="n">
+        <v>35.59036144578313</v>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1099" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1099" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1099" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>192.json</t>
+        </is>
+      </c>
+      <c r="D1100" t="n">
+        <v>37.99763681506738</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>33985</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>201</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>63</v>
+      </c>
+      <c r="H1100" t="n">
+        <v>30.49206349206349</v>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1100" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1100" t="n">
+        <v>58</v>
+      </c>
+      <c r="L1100" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>193.json</t>
+        </is>
+      </c>
+      <c r="D1101" t="n">
+        <v>48.38555583613925</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>39241</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>243</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>85</v>
+      </c>
+      <c r="H1101" t="n">
+        <v>26.49411764705882</v>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1101" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1101" t="n">
+        <v>24</v>
+      </c>
+      <c r="L1101" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>194.json</t>
+        </is>
+      </c>
+      <c r="D1102" t="n">
+        <v>99.59151404595468</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>124718</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>536</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>70</v>
+      </c>
+      <c r="H1102" t="n">
+        <v>37.12857142857143</v>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1102" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1102" t="n">
+        <v>34</v>
+      </c>
+      <c r="L1102" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>195.json</t>
+        </is>
+      </c>
+      <c r="D1103" t="n">
+        <v>5.266611270024441</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>3752</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1103" t="n">
+        <v>33.26666666666667</v>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1103" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1103" t="n">
+        <v>13</v>
+      </c>
+      <c r="L1103" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>196.json</t>
+        </is>
+      </c>
+      <c r="D1104" t="n">
+        <v>18.34919705992797</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>12141</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>95</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1104" t="n">
+        <v>33.2962962962963</v>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1104" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1104" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1104" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>197.json</t>
+        </is>
+      </c>
+      <c r="D1105" t="n">
+        <v>10.63844916102244</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>10415</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1105" t="n">
+        <v>80.84210526315789</v>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1105" t="inlineStr">
+        <is>
+          <t>bash</t>
+        </is>
+      </c>
+      <c r="K1105" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1105" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>198.json</t>
+        </is>
+      </c>
+      <c r="D1106" t="n">
+        <v>39.61027309414931</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>35665</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>184</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1106" t="n">
+        <v>28.39285714285714</v>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1106" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1106" t="n">
+        <v>11</v>
+      </c>
+      <c r="L1106" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>199.json</t>
+        </is>
+      </c>
+      <c r="D1107" t="n">
+        <v>13.46783144003712</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>14833</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1107" t="n">
+        <v>55.61904761904762</v>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1107" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1107" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1107" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>200.json</t>
+        </is>
+      </c>
+      <c r="D1108" t="n">
+        <v>20.05611354025314</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>19631</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>103</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1108" t="n">
+        <v>68.59090909090909</v>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1108" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1108" t="n">
+        <v>13</v>
+      </c>
+      <c r="L1108" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>201.json</t>
+        </is>
+      </c>
+      <c r="D1109" t="n">
+        <v>9.126441332977265</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>31621</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>94</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1109" t="n">
+        <v>54.13636363636363</v>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1109" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1109" t="n">
+        <v>12</v>
+      </c>
+      <c r="L1109" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>202.json</t>
+        </is>
+      </c>
+      <c r="D1110" t="n">
+        <v>21.08165545598604</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>27360</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>138</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1110" t="n">
+        <v>42</v>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1110" t="inlineStr">
+        <is>
+          <t>bash</t>
+        </is>
+      </c>
+      <c r="K1110" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1110" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>203.json</t>
+        </is>
+      </c>
+      <c r="D1111" t="n">
+        <v>24.11573648592457</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>22647</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>101</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1111" t="n">
+        <v>41.74193548387097</v>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1111" t="n">
+        <v>15</v>
+      </c>
+      <c r="L1111" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>204.json</t>
+        </is>
+      </c>
+      <c r="D1112" t="n">
+        <v>69.57173211593181</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>107682</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1112" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1112" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1112" t="n">
+        <v>21</v>
+      </c>
+      <c r="L1112" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>205.json</t>
+        </is>
+      </c>
+      <c r="D1113" t="n">
+        <v>10.08633896696847</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>10776</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1113" t="n">
+        <v>42.52380952380953</v>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1113" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1113" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>206.json</t>
+        </is>
+      </c>
+      <c r="D1114" t="n">
+        <v>7.730957555002533</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>6347</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1114" t="n">
+        <v>31.35294117647059</v>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>bash</t>
+        </is>
+      </c>
+      <c r="K1114" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1114" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>207.json</t>
+        </is>
+      </c>
+      <c r="D1115" t="n">
+        <v>12.81806492817122</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>7062</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>63</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1115" t="n">
+        <v>48.73214285714285</v>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1115" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1115" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>208.json</t>
+        </is>
+      </c>
+      <c r="D1116" t="n">
+        <v>73.84384212101577</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>95130</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>375</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1116" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1116" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1116" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>209.json</t>
+        </is>
+      </c>
+      <c r="D1117" t="n">
+        <v>35.47269230388338</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>38422</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>171</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1117" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1117" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1117" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>210.json</t>
+        </is>
+      </c>
+      <c r="D1118" t="n">
+        <v>33.61904631298967</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>36928</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1118" t="n">
+        <v>32</v>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1118" t="n">
+        <v>6</v>
+      </c>
+      <c r="L1118" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>211.json</t>
+        </is>
+      </c>
+      <c r="D1119" t="n">
+        <v>25.61325796926394</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>22466</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>133</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1119" t="n">
+        <v>40.94444444444444</v>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+      <c r="K1119" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1119" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>212.json</t>
+        </is>
+      </c>
+      <c r="D1120" t="n">
+        <v>115.7296725098277</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>197812</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>560</v>
+      </c>
+      <c r="G1120" t="n">
+        <v>78</v>
+      </c>
+      <c r="H1120" t="n">
+        <v>42</v>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1120" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1120" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>213.json</t>
+        </is>
+      </c>
+      <c r="D1121" t="n">
+        <v>85.85391194664408</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>286562</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>549</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>80</v>
+      </c>
+      <c r="H1121" t="n">
+        <v>40.6875</v>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1121" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1121" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>214.json</t>
+        </is>
+      </c>
+      <c r="D1122" t="n">
+        <v>5.662757109035738</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>4139</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1122" t="n">
+        <v>53.63157894736842</v>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1122" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1122" t="n">
+        <v>14</v>
+      </c>
+      <c r="L1122" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>215.json</t>
+        </is>
+      </c>
+      <c r="D1123" t="n">
+        <v>36.09380620485172</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>23353</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>139</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1123" t="n">
+        <v>50.71428571428572</v>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1123" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1123" t="n">
+        <v>17</v>
+      </c>
+      <c r="L1123" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>216.json</t>
+        </is>
+      </c>
+      <c r="D1124" t="n">
+        <v>33.6410439190222</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>27400</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1124" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1124" t="inlineStr">
+        <is>
+          <t>bash</t>
+        </is>
+      </c>
+      <c r="K1124" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1124" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>217.json</t>
+        </is>
+      </c>
+      <c r="D1125" t="n">
+        <v>16.27144102205057</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>11445</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>110</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1125" t="n">
+        <v>53.14634146341464</v>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1125" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1125" t="n">
+        <v>37</v>
+      </c>
+      <c r="L1125" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>218.json</t>
+        </is>
+      </c>
+      <c r="D1126" t="n">
+        <v>17.84060416789725</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>10095</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>97</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1126" t="n">
+        <v>58</v>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1126" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1126" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1126" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>trace_elephant</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>219.json</t>
+        </is>
+      </c>
+      <c r="D1127" t="n">
+        <v>112.3559166938066</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>168291</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>618</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>88</v>
+      </c>
+      <c r="H1127" t="n">
+        <v>28.875</v>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J1127" t="inlineStr">
+        <is>
+          <t>str_replace_editor</t>
+        </is>
+      </c>
+      <c r="K1127" t="n">
+        <v>24</v>
+      </c>
+      <c r="L1127" t="inlineStr">
+        <is>
+          <t>step_by_step</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
